--- a/templates/06-participant-tracker.xlsx
+++ b/templates/06-participant-tracker.xlsx
@@ -28,32 +28,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="IBM Plex Sans"/>
+      <name val="Public Sans"/>
       <b val="1"/>
-      <color rgb="000F62FE"/>
+      <color rgb="00005EA2"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="IBM Plex Sans"/>
-      <color rgb="00161616"/>
+      <name val="Public Sans"/>
+      <color rgb="001B1B1B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="IBM Plex Sans"/>
+      <name val="Public Sans"/>
       <b val="1"/>
-      <color rgb="000F62FE"/>
+      <color rgb="00005EA2"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="IBM Plex Sans"/>
+      <name val="Public Sans"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="IBM Plex Sans"/>
+      <name val="Public Sans"/>
       <i val="1"/>
-      <color rgb="00525252"/>
+      <color rgb="00565C65"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -66,12 +66,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F62FE"/>
+        <fgColor rgb="00005EA2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F4F4"/>
+        <fgColor rgb="00F0F0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,16 +85,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00DFE1E2"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00DFE1E2"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00DFE1E2"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00DFE1E2"/>
       </bottom>
     </border>
   </borders>
@@ -597,8 +597,8 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;"IBM Plex Sans,Bold"&amp;9 UX Research</oddHeader>
-    <oddFooter>&amp;R&amp;"IBM Plex Sans"&amp;9 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Public Sans,Bold"&amp;9 UX Research</oddHeader>
+    <oddFooter>&amp;R&amp;"Public Sans"&amp;9 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1607,8 +1607,8 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;"IBM Plex Sans,Bold"&amp;9 UX Research</oddHeader>
-    <oddFooter>&amp;R&amp;"IBM Plex Sans"&amp;9 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Public Sans,Bold"&amp;9 UX Research</oddHeader>
+    <oddFooter>&amp;R&amp;"Public Sans"&amp;9 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2732,8 +2732,8 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;"IBM Plex Sans,Bold"&amp;9 UX Research</oddHeader>
-    <oddFooter>&amp;R&amp;"IBM Plex Sans"&amp;9 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Public Sans,Bold"&amp;9 UX Research</oddHeader>
+    <oddFooter>&amp;R&amp;"Public Sans"&amp;9 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/templates/06-participant-tracker.xlsx
+++ b/templates/06-participant-tracker.xlsx
@@ -30,18 +30,18 @@
     <font>
       <name val="Public Sans"/>
       <b val="1"/>
-      <color rgb="00005EA2"/>
+      <color rgb="00002436"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Public Sans"/>
-      <color rgb="001B1B1B"/>
+      <color rgb="001F2A30"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Public Sans"/>
       <b val="1"/>
-      <color rgb="00005EA2"/>
+      <color rgb="00002436"/>
       <sz val="11"/>
     </font>
     <font>
@@ -53,7 +53,7 @@
     <font>
       <name val="Public Sans"/>
       <i val="1"/>
-      <color rgb="00565C65"/>
+      <color rgb="005C6670"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -66,12 +66,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00005EA2"/>
+        <fgColor rgb="00002436"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
+        <fgColor rgb="00E3E8EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,16 +85,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00DFE1E2"/>
+        <color rgb="00D4D8D9"/>
       </left>
       <right style="thin">
-        <color rgb="00DFE1E2"/>
+        <color rgb="00D4D8D9"/>
       </right>
       <top style="thin">
-        <color rgb="00DFE1E2"/>
+        <color rgb="00D4D8D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00DFE1E2"/>
+        <color rgb="00D4D8D9"/>
       </bottom>
     </border>
   </borders>
